--- a/02-tailspin-civic-rev5-ato/artifacts/poam.xlsx
+++ b/02-tailspin-civic-rev5-ato/artifacts/poam.xlsx
@@ -605,6 +605,7 @@
     <col width="10" customWidth="1" style="17" min="16" max="16"/>
     <col width="11" customWidth="1" style="17" min="17" max="17"/>
     <col width="24" customWidth="1" style="17" min="18" max="18"/>
+    <col width="15" customWidth="1" style="18" min="19" max="19"/>
     <col width="20" customWidth="1" style="17" min="20" max="20"/>
     <col width="14" customWidth="1" style="17" min="21" max="21"/>
   </cols>
@@ -621,13 +622,13 @@
         </is>
       </c>
       <c r="U1" s="21" t="n">
-        <v>46112</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="18">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>AwardWorks Platform (SaaS) | FedRAMP Moderate | Reporting Period: Q1 2026 | Status Date: 2026-03-31 | Fictional organization. Created for portfolio demonstration purposes.</t>
+          <t>AwardWorks Platform (SaaS) | FedRAMP Moderate | Reporting Period: Q1 2026 | Status Date: 2026-03-27 | Fictional organization. Created for portfolio demonstration purposes.</t>
         </is>
       </c>
     </row>
@@ -722,6 +723,11 @@
           <t>Deviation / Risk Acceptance</t>
         </is>
       </c>
+      <c r="S4" s="23" t="inlineStr">
+        <is>
+          <t>Original Detection Date</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="68.65000000000001" customHeight="1" s="18">
       <c r="A5" s="24" t="inlineStr">
@@ -785,11 +791,11 @@
         </is>
       </c>
       <c r="M5" s="25" t="n">
-        <v>46203</v>
+        <v>46198</v>
       </c>
       <c r="N5" s="24" t="inlineStr">
         <is>
-          <t>M1: Remediate all open High findings (2026-05-15); M2: Deploy automated SLA escalation (2026-06-15); M3: Validate with clean scan cycle (2026-06-30)</t>
+          <t>M1: Remediate all open High findings (2026-05-18); M2: Deploy automated SLA escalation (2026-06-22); M3: Validate with clean scan cycle (2026-06-25)</t>
         </is>
       </c>
       <c r="O5" s="24" t="inlineStr">
@@ -798,14 +804,21 @@
         </is>
       </c>
       <c r="P5" s="24">
-        <f>IF(O5="Closed","",MAX(0,$U$1-DATE(2026,3,1)))</f>
+        <f>IF(O5="Closed","",MAX(0,$U$1-S5))</f>
         <v/>
       </c>
       <c r="Q5" s="24">
         <f>IF(O5="Closed","No",IF(M5&lt;$U$1,"YES","No"))</f>
         <v/>
       </c>
-      <c r="R5" s="24" t="n"/>
+      <c r="R5" s="24" t="inlineStr">
+        <is>
+          <t>Scheduled completion exceeds the 30-day High remediation window. The AO accepted the schedule as an authorization condition (SAR §5); any missed milestone requires a deviation request.</t>
+        </is>
+      </c>
+      <c r="S5" s="25" t="n">
+        <v>46043</v>
+      </c>
     </row>
     <row r="6" ht="57.45" customHeight="1" s="18">
       <c r="A6" s="24" t="inlineStr">
@@ -869,11 +882,11 @@
         </is>
       </c>
       <c r="M6" s="25" t="n">
-        <v>46173</v>
+        <v>46169</v>
       </c>
       <c r="N6" s="24" t="inlineStr">
         <is>
-          <t>M1: Re-image affected hosts (2026-04-15); M2: Enable Config auto-remediation rules (2026-05-15); M3: Add pre-deploy drift gate to CI (2026-05-31)</t>
+          <t>M1: Re-image affected hosts (2026-04-17); M2: Enable Config auto-remediation rules (2026-05-18); M3: Add pre-deploy drift gate to CI (2026-05-27)</t>
         </is>
       </c>
       <c r="O6" s="24" t="inlineStr">
@@ -882,7 +895,7 @@
         </is>
       </c>
       <c r="P6" s="24">
-        <f>IF(O6="Closed","",MAX(0,$U$1-DATE(2026,3,1)))</f>
+        <f>IF(O6="Closed","",MAX(0,$U$1-S6))</f>
         <v/>
       </c>
       <c r="Q6" s="24">
@@ -890,6 +903,9 @@
         <v/>
       </c>
       <c r="R6" s="24" t="n"/>
+      <c r="S6" s="25" t="n">
+        <v>46063</v>
+      </c>
     </row>
     <row r="7" ht="46.25" customHeight="1" s="18">
       <c r="A7" s="24" t="inlineStr">
@@ -914,7 +930,7 @@
       </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>AC-6(9), AU-2</t>
+          <t>AC-6(9)</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
@@ -953,11 +969,11 @@
         </is>
       </c>
       <c r="M7" s="25" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="N7" s="24" t="inlineStr">
         <is>
-          <t>M1: Deploy forwarding agent (2026-04-20); M2: Validate event coverage (2026-05-05); M3: Confirm SIEM alerting rules fire (2026-05-15)</t>
+          <t>M1: Deploy forwarding agent (2026-04-20); M2: Validate event coverage (2026-05-05); M3: Confirm SIEM alerting rules fire (2026-05-18)</t>
         </is>
       </c>
       <c r="O7" s="24" t="inlineStr">
@@ -966,7 +982,7 @@
         </is>
       </c>
       <c r="P7" s="24">
-        <f>IF(O7="Closed","",MAX(0,$U$1-DATE(2026,3,1)))</f>
+        <f>IF(O7="Closed","",MAX(0,$U$1-S7))</f>
         <v/>
       </c>
       <c r="Q7" s="24">
@@ -974,6 +990,9 @@
         <v/>
       </c>
       <c r="R7" s="24" t="n"/>
+      <c r="S7" s="25" t="n">
+        <v>46057</v>
+      </c>
     </row>
     <row r="8" ht="68.65000000000001" customHeight="1" s="18">
       <c r="A8" s="24" t="inlineStr">
@@ -1013,7 +1032,7 @@
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="I8" s="24" t="inlineStr">
@@ -1037,11 +1056,11 @@
         </is>
       </c>
       <c r="M8" s="25" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="N8" s="24" t="inlineStr">
         <is>
-          <t>M1: Develop exercise scenario and success criteria (2026-05-30); M2: Execute recovery exercise (2026-07-15); M3: Update Contingency Plan and after-action report (2026-07-31)</t>
+          <t>M1: Develop exercise scenario and success criteria (2026-05-26); M2: Execute recovery exercise (2026-07-20); M3: Update Contingency Plan and after-action report (2026-07-27)</t>
         </is>
       </c>
       <c r="O8" s="24" t="inlineStr">
@@ -1050,7 +1069,7 @@
         </is>
       </c>
       <c r="P8" s="24">
-        <f>IF(O8="Closed","",MAX(0,$U$1-DATE(2026,3,1)))</f>
+        <f>IF(O8="Closed","",MAX(0,$U$1-S8))</f>
         <v/>
       </c>
       <c r="Q8" s="24">
@@ -1058,6 +1077,9 @@
         <v/>
       </c>
       <c r="R8" s="24" t="n"/>
+      <c r="S8" s="25" t="n">
+        <v>46071</v>
+      </c>
     </row>
     <row r="9" ht="57.45" customHeight="1" s="18">
       <c r="A9" s="24" t="inlineStr">
@@ -1121,11 +1143,11 @@
         </is>
       </c>
       <c r="M9" s="25" t="n">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="N9" s="24" t="inlineStr">
         <is>
-          <t>M1: Build ticketed review workflow (2026-04-10); M2: Complete four consecutive evidenced review cycles (2026-04-30)</t>
+          <t>M1: Build ticketed review workflow (2026-04-10); M2: Complete four consecutive evidenced review cycles (2026-04-27)</t>
         </is>
       </c>
       <c r="O9" s="24" t="inlineStr">
@@ -1134,7 +1156,7 @@
         </is>
       </c>
       <c r="P9" s="24">
-        <f>IF(O9="Closed","",MAX(0,$U$1-DATE(2026,3,1)))</f>
+        <f>IF(O9="Closed","",MAX(0,$U$1-S9))</f>
         <v/>
       </c>
       <c r="Q9" s="24">
@@ -1142,8 +1164,11 @@
         <v/>
       </c>
       <c r="R9" s="24" t="n"/>
-    </row>
-    <row r="10" ht="260" customHeight="1" s="18">
+      <c r="S9" s="25" t="n">
+        <v>46050</v>
+      </c>
+    </row>
+    <row r="10" ht="57.45" customHeight="1" s="18">
       <c r="A10" s="24" t="inlineStr">
         <is>
           <t>V-006</t>
@@ -1156,7 +1181,7 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>The one-hour US-CERT and FedRAMP ISSO incident notification requirement is documented in the Incident Response Plan but has not been validated through a tabletop or live exercise, creating uncertainty about the organization's ability to meet the timeline.</t>
+          <t>The one-hour CISA and agency ISSO incident notification requirement is documented in the Incident Response Plan but has not been validated through a tabletop or live exercise, creating uncertainty about the organization's ability to meet the timeline.</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
@@ -1166,7 +1191,7 @@
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>IR-6, IR-4</t>
+          <t>IR-6</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
@@ -1201,15 +1226,15 @@
       </c>
       <c r="L10" s="24" t="inlineStr">
         <is>
-          <t>Conduct a tabletop exercise specifically testing notification timelines to US-CERT and the FedRAMP ISSO; document actual elapsed times; update the IR Plan and contact roster based on results.</t>
+          <t>Conduct a tabletop exercise specifically testing notification timelines to CISA and the agency ISSO; document actual elapsed times; update the IR Plan and contact roster based on results.</t>
         </is>
       </c>
       <c r="M10" s="25" t="n">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="N10" s="24" t="inlineStr">
         <is>
-          <t>M1: Develop tabletop scenario (2026-05-01); M2: Execute tabletop with Legal and Communications (2026-06-01); M3: Update IR Plan and roster (2026-06-15) Later evidence (AAR approved 2026-06-04, sections 8–11): original 2026-06-15 completion is incompatible with corrective actions due 2026-06-30 and 2026-07-15. Reason: notification draft took 64 minutes against 60; severity classification was delayed. Follow-up exercise recommended by 2026-09-30. Original date retained; approved revised closure date not recorded.</t>
+          <t>M1: Develop tabletop scenario (2026-05-08); M2: Execute tabletop with Legal and Communications (2026-06-02); M3: Update IR Plan and roster (2026-06-22)</t>
         </is>
       </c>
       <c r="O10" s="24" t="inlineStr">
@@ -1218,7 +1243,7 @@
         </is>
       </c>
       <c r="P10" s="24">
-        <f>IF(O10="Closed","",MAX(0,$U$1-DATE(2026,3,1)))</f>
+        <f>IF(O10="Closed","",MAX(0,$U$1-S10))</f>
         <v/>
       </c>
       <c r="Q10" s="24">
@@ -1226,6 +1251,9 @@
         <v/>
       </c>
       <c r="R10" s="24" t="n"/>
+      <c r="S10" s="25" t="n">
+        <v>46072</v>
+      </c>
     </row>
     <row r="11" ht="57.45" customHeight="1" s="18">
       <c r="A11" s="24" t="inlineStr">
@@ -1289,11 +1317,11 @@
         </is>
       </c>
       <c r="M11" s="25" t="n">
-        <v>46173</v>
+        <v>46169</v>
       </c>
       <c r="N11" s="24" t="inlineStr">
         <is>
-          <t>M1: Automate deliverable package generation (2026-05-01); M2: Establish internal deadline and backup owner (2026-05-15); M3: Two consecutive on-time cycles (2026-05-31)</t>
+          <t>M1: Automate deliverable package generation (2026-05-08); M2: Establish internal deadline and backup owner (2026-05-18); M3: Two consecutive on-time cycles (2026-05-27)</t>
         </is>
       </c>
       <c r="O11" s="24" t="inlineStr">
@@ -1302,7 +1330,7 @@
         </is>
       </c>
       <c r="P11" s="24">
-        <f>IF(O11="Closed","",MAX(0,$U$1-DATE(2026,3,1)))</f>
+        <f>IF(O11="Closed","",MAX(0,$U$1-S11))</f>
         <v/>
       </c>
       <c r="Q11" s="24">
@@ -1310,6 +1338,9 @@
         <v/>
       </c>
       <c r="R11" s="24" t="n"/>
+      <c r="S11" s="25" t="n">
+        <v>46007</v>
+      </c>
     </row>
     <row r="12" ht="57.45" customHeight="1" s="18">
       <c r="A12" s="24" t="inlineStr">
@@ -1334,7 +1365,7 @@
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>AC-2, AC-6</t>
+          <t>AC-2</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
@@ -1344,7 +1375,7 @@
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -1354,7 +1385,7 @@
       </c>
       <c r="I12" s="24" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J12" s="24" t="inlineStr">
@@ -1373,11 +1404,11 @@
         </is>
       </c>
       <c r="M12" s="25" t="n">
-        <v>46265</v>
+        <v>46261</v>
       </c>
       <c r="N12" s="24" t="inlineStr">
         <is>
-          <t>M1: Inventory required privileges per job (2026-05-30); M2: Create scoped roles and migrate jobs (2026-07-31); M3: Disable shared account and validate logs (2026-08-31)</t>
+          <t>M1: Inventory required privileges per job (2026-05-26); M2: Create scoped roles and migrate jobs (2026-07-27); M3: Disable shared account and validate logs (2026-08-27)</t>
         </is>
       </c>
       <c r="O12" s="24" t="inlineStr">
@@ -1386,14 +1417,21 @@
         </is>
       </c>
       <c r="P12" s="24">
-        <f>IF(O12="Closed","",MAX(0,$U$1-DATE(2026,3,1)))</f>
+        <f>IF(O12="Closed","",MAX(0,$U$1-S12))</f>
         <v/>
       </c>
       <c r="Q12" s="24">
         <f>IF(O12="Closed","No",IF(M12&lt;$U$1,"YES","No"))</f>
         <v/>
       </c>
-      <c r="R12" s="24" t="n"/>
+      <c r="R12" s="24" t="inlineStr">
+        <is>
+          <t>High-risk item scheduled beyond 30 days; tracked as an authorization condition (SAR §5) rather than a formal deviation.</t>
+        </is>
+      </c>
+      <c r="S12" s="25" t="n">
+        <v>46000</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1694,7 +1732,7 @@
       </c>
       <c r="B5" s="32" t="inlineStr">
         <is>
-          <t>Derived from Likelihood and Impact. FedRAMP remediation timelines: High = 30 days, Moderate = 90 days, Low = 180 days from discovery.</t>
+          <t>Risk Rating is derived from Likelihood and Impact using the NIST SP 800-30 Rev. 1 Table I-2 matrix. FedRAMP remediation timelines for scan-identified vulnerabilities: High = 30 days, Moderate = 90 days, Low = 180 days from the Original Detection Date. Days Open counts from that date to the Status Date.</t>
         </is>
       </c>
     </row>
